--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-11).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-11).xlsx
@@ -932,22 +932,25 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>R$ 9.178,14</t>
-  </si>
-  <si>
-    <t>97.9</t>
-  </si>
-  <si>
-    <t>61.0</t>
-  </si>
-  <si>
-    <t>6.48</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 9.128,90</t>
+  </si>
+  <si>
+    <t>97.5</t>
+  </si>
+  <si>
+    <t>61.3</t>
+  </si>
+  <si>
+    <t>6.45</t>
   </si>
   <si>
     <t>21.4</t>
@@ -956,13 +959,13 @@
     <t>8.2</t>
   </si>
   <si>
-    <t>5.9</t>
-  </si>
-  <si>
-    <t>34.1%</t>
-  </si>
-  <si>
-    <t>16.5%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>33.6%</t>
+  </si>
+  <si>
+    <t>16.6%</t>
   </si>
   <si>
     <t>0.9%</t>
@@ -974,52 +977,52 @@
     <t>3.2%</t>
   </si>
   <si>
-    <t>0.8%</t>
-  </si>
-  <si>
-    <t>5.9%</t>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>6.0%</t>
   </si>
   <si>
     <t>2.7%</t>
   </si>
   <si>
-    <t>5.4%</t>
-  </si>
-  <si>
-    <t>2081.0</t>
-  </si>
-  <si>
-    <t>1768.0</t>
-  </si>
-  <si>
-    <t>97.0</t>
+    <t>5.5%</t>
+  </si>
+  <si>
+    <t>2229.0</t>
+  </si>
+  <si>
+    <t>1894.0</t>
+  </si>
+  <si>
+    <t>103.0</t>
   </si>
   <si>
     <t>16.0</t>
   </si>
   <si>
-    <t>348.0</t>
-  </si>
-  <si>
-    <t>84.0</t>
+    <t>363.0</t>
+  </si>
+  <si>
+    <t>85.0</t>
   </si>
   <si>
     <t>14.0</t>
   </si>
   <si>
-    <t>638.0</t>
-  </si>
-  <si>
-    <t>286.0</t>
-  </si>
-  <si>
-    <t>577.0</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>37.0</t>
+    <t>686.0</t>
+  </si>
+  <si>
+    <t>310.0</t>
+  </si>
+  <si>
+    <t>625.0</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>43.0</t>
   </si>
   <si>
     <t>1</t>
@@ -3275,7 +3278,9 @@
       <c r="N13" s="6">
         <v>131</v>
       </c>
-      <c r="O13" s="6"/>
+      <c r="O13" s="6">
+        <v>99</v>
+      </c>
       <c r="P13" s="7">
         <v>8.750890839694657</v>
       </c>
@@ -3285,31 +3290,75 @@
       <c r="R13" s="8">
         <v>5.3188555555555554</v>
       </c>
-      <c r="S13" s="8"/>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
       <c r="T13" s="9">
         <v>0.19191919191919191</v>
       </c>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="U13" s="9">
+        <v>0.12121212121212122</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.030303030303030304</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.030303030303030304</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.040404040404040407</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>12</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0.020202020202020204</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>2</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -6368,7 +6417,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>51</v>
@@ -6398,35 +6447,93 @@
         <v>58</v>
       </c>
       <c r="L34" s="4"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9"/>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-      <c r="AA34" s="9"/>
-      <c r="AB34" s="9"/>
-      <c r="AC34" s="9"/>
-      <c r="AD34" s="6"/>
-      <c r="AE34" s="6"/>
-      <c r="AF34" s="6"/>
-      <c r="AG34" s="6"/>
-      <c r="AH34" s="6"/>
-      <c r="AI34" s="6"/>
-      <c r="AJ34" s="6"/>
-      <c r="AK34" s="6"/>
-      <c r="AL34" s="6"/>
-      <c r="AM34" s="6"/>
-      <c r="AN34" s="9"/>
-      <c r="AO34" s="6"/>
+      <c r="M34" s="5">
+        <v>13297.469999999999</v>
+      </c>
+      <c r="N34" s="6">
+        <v>177</v>
+      </c>
+      <c r="O34" s="6">
+        <v>147</v>
+      </c>
+      <c r="P34" s="7">
+        <v>6.816193181818182</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>15.317573469387757</v>
+      </c>
+      <c r="R34" s="8">
+        <v>2.1063220689655173</v>
+      </c>
+      <c r="S34" s="8">
+        <v>6</v>
+      </c>
+      <c r="T34" s="9">
+        <v>0.55782312925170063</v>
+      </c>
+      <c r="U34" s="9">
+        <v>0.40136054421768708</v>
+      </c>
+      <c r="V34" s="9">
+        <v>0</v>
+      </c>
+      <c r="W34" s="9">
+        <v>0</v>
+      </c>
+      <c r="X34" s="9">
+        <v>0.0068027210884353739</v>
+      </c>
+      <c r="Y34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="9">
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="AB34" s="9">
+        <v>0.081632653061224483</v>
+      </c>
+      <c r="AC34" s="9">
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="AD34" s="6">
+        <v>76</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>59</v>
+      </c>
+      <c r="AF34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="6">
+        <v>35</v>
+      </c>
+      <c r="AL34" s="6">
+        <v>12</v>
+      </c>
+      <c r="AM34" s="6">
+        <v>28</v>
+      </c>
+      <c r="AN34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP34" s="4">
         <v>58</v>
       </c>
@@ -6624,7 +6731,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6654,35 +6761,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>5620.4799999999996</v>
+      </c>
+      <c r="N36" s="6">
+        <v>68</v>
+      </c>
+      <c r="O36" s="6">
+        <v>57</v>
+      </c>
+      <c r="P36" s="7">
+        <v>5.0260869565217394</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>16.640057894736842</v>
+      </c>
+      <c r="R36" s="8">
+        <v>4.6786543859649115</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.43859649122807015</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.035087719298245612</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0.035087719298245612</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7506,7 +7671,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7536,35 +7701,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>5819.6700000000001</v>
+      </c>
+      <c r="N42" s="6">
+        <v>52</v>
+      </c>
+      <c r="O42" s="6">
+        <v>34</v>
+      </c>
+      <c r="P42" s="7">
+        <v>5.2871788461538456</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>21.148529411764706</v>
+      </c>
+      <c r="R42" s="8">
+        <v>8.5205882352941167</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.14705882352941177</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -12526,7 +12749,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12554,35 +12777,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>10914.24</v>
+      </c>
+      <c r="N76" s="6">
+        <v>130</v>
+      </c>
+      <c r="O76" s="6">
+        <v>77</v>
+      </c>
+      <c r="P76" s="7">
+        <v>4.5643592307692309</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>21.86017272727273</v>
+      </c>
+      <c r="R76" s="8">
+        <v>8.89054054054054</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.20779220779220781</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.025974025974025976</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.1038961038961039</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.07792207792207792</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>8</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -18400,33 +18681,79 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
+      <c r="O116" s="6">
+        <v>53</v>
+      </c>
       <c r="P116" s="7"/>
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
-      <c r="S116" s="8"/>
+      <c r="S116" s="8">
+        <v>7</v>
+      </c>
       <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
-      <c r="V116" s="9"/>
-      <c r="W116" s="9"/>
-      <c r="X116" s="9"/>
-      <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-      <c r="AA116" s="9"/>
-      <c r="AB116" s="9"/>
-      <c r="AC116" s="9"/>
-      <c r="AD116" s="6"/>
-      <c r="AE116" s="6"/>
-      <c r="AF116" s="6"/>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="6"/>
-      <c r="AI116" s="6"/>
-      <c r="AJ116" s="6"/>
-      <c r="AK116" s="6"/>
-      <c r="AL116" s="6"/>
-      <c r="AM116" s="6"/>
-      <c r="AN116" s="9"/>
-      <c r="AO116" s="6"/>
+      <c r="U116" s="9">
+        <v>0.13207547169811321</v>
+      </c>
+      <c r="V116" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="W116" s="9">
+        <v>0</v>
+      </c>
+      <c r="X116" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="Y116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="9">
+        <v>0.037735849056603772</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN116" s="9">
+        <v>0.037735849056603772</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>2</v>
+      </c>
       <c t="s" r="AP116" s="4">
         <v>58</v>
       </c>
@@ -21444,7 +21771,7 @@
         <v>19785</v>
       </c>
       <c r="B136" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C136" s="4">
         <v>51</v>
@@ -21474,35 +21801,93 @@
         <v>58</v>
       </c>
       <c r="L136" s="4"/>
-      <c r="M136" s="5"/>
-      <c r="N136" s="6"/>
-      <c r="O136" s="6"/>
-      <c r="P136" s="7"/>
-      <c r="Q136" s="8"/>
-      <c r="R136" s="8"/>
-      <c r="S136" s="8"/>
-      <c r="T136" s="9"/>
-      <c r="U136" s="9"/>
-      <c r="V136" s="9"/>
-      <c r="W136" s="9"/>
-      <c r="X136" s="9"/>
-      <c r="Y136" s="9"/>
-      <c r="Z136" s="9"/>
-      <c r="AA136" s="9"/>
-      <c r="AB136" s="9"/>
-      <c r="AC136" s="9"/>
-      <c r="AD136" s="6"/>
-      <c r="AE136" s="6"/>
-      <c r="AF136" s="6"/>
-      <c r="AG136" s="6"/>
-      <c r="AH136" s="6"/>
-      <c r="AI136" s="6"/>
-      <c r="AJ136" s="6"/>
-      <c r="AK136" s="6"/>
-      <c r="AL136" s="6"/>
-      <c r="AM136" s="6"/>
-      <c r="AN136" s="9"/>
-      <c r="AO136" s="6"/>
+      <c r="M136" s="5">
+        <v>11214.24</v>
+      </c>
+      <c r="N136" s="6">
+        <v>97</v>
+      </c>
+      <c r="O136" s="6">
+        <v>54</v>
+      </c>
+      <c r="P136" s="7">
+        <v>6.8192443298969065</v>
+      </c>
+      <c r="Q136" s="8">
+        <v>34.597222222222221</v>
+      </c>
+      <c r="R136" s="8">
+        <v>21.10709814814815</v>
+      </c>
+      <c r="S136" s="8">
+        <v>7</v>
+      </c>
+      <c r="T136" s="9">
+        <v>0.092592592592592587</v>
+      </c>
+      <c r="U136" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="V136" s="9">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="W136" s="9">
+        <v>0</v>
+      </c>
+      <c r="X136" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y136" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="9">
+        <v>0.018518518518518517</v>
+      </c>
+      <c r="AB136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC136" s="9">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="AD136" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE136" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF136" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK136" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM136" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO136" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP136" s="4">
         <v>58</v>
       </c>
@@ -22109,7 +22494,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>51</v>
@@ -22139,35 +22524,93 @@
         <v>58</v>
       </c>
       <c r="L141" s="4"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="6"/>
-      <c r="O141" s="6"/>
-      <c r="P141" s="7"/>
-      <c r="Q141" s="8"/>
-      <c r="R141" s="8"/>
-      <c r="S141" s="8"/>
-      <c r="T141" s="9"/>
-      <c r="U141" s="9"/>
-      <c r="V141" s="9"/>
-      <c r="W141" s="9"/>
-      <c r="X141" s="9"/>
-      <c r="Y141" s="9"/>
-      <c r="Z141" s="9"/>
-      <c r="AA141" s="9"/>
-      <c r="AB141" s="9"/>
-      <c r="AC141" s="9"/>
-      <c r="AD141" s="6"/>
-      <c r="AE141" s="6"/>
-      <c r="AF141" s="6"/>
-      <c r="AG141" s="6"/>
-      <c r="AH141" s="6"/>
-      <c r="AI141" s="6"/>
-      <c r="AJ141" s="6"/>
-      <c r="AK141" s="6"/>
-      <c r="AL141" s="6"/>
-      <c r="AM141" s="6"/>
-      <c r="AN141" s="9"/>
-      <c r="AO141" s="6"/>
+      <c r="M141" s="5">
+        <v>5529.8999999999996</v>
+      </c>
+      <c r="N141" s="6">
+        <v>60</v>
+      </c>
+      <c r="O141" s="6">
+        <v>32</v>
+      </c>
+      <c r="P141" s="7">
+        <v>3.2758620689655173</v>
+      </c>
+      <c r="Q141" s="8">
+        <v>15.737500000000001</v>
+      </c>
+      <c r="R141" s="8">
+        <v>4.5250000000000004</v>
+      </c>
+      <c r="S141" s="8">
+        <v>8</v>
+      </c>
+      <c r="T141" s="9">
+        <v>0.5625</v>
+      </c>
+      <c r="U141" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="V141" s="9">
+        <v>0</v>
+      </c>
+      <c r="W141" s="9">
+        <v>0</v>
+      </c>
+      <c r="X141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AB141" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AC141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD141" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO141" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP141" s="4">
         <v>58</v>
       </c>
@@ -28897,7 +29340,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>51</v>
@@ -28927,35 +29370,93 @@
         <v>58</v>
       </c>
       <c r="L187" s="4"/>
-      <c r="M187" s="5"/>
-      <c r="N187" s="6"/>
-      <c r="O187" s="6"/>
-      <c r="P187" s="7"/>
-      <c r="Q187" s="8"/>
-      <c r="R187" s="8"/>
-      <c r="S187" s="8"/>
-      <c r="T187" s="9"/>
-      <c r="U187" s="9"/>
-      <c r="V187" s="9"/>
-      <c r="W187" s="9"/>
-      <c r="X187" s="9"/>
-      <c r="Y187" s="9"/>
-      <c r="Z187" s="9"/>
-      <c r="AA187" s="9"/>
-      <c r="AB187" s="9"/>
-      <c r="AC187" s="9"/>
-      <c r="AD187" s="6"/>
-      <c r="AE187" s="6"/>
-      <c r="AF187" s="6"/>
-      <c r="AG187" s="6"/>
-      <c r="AH187" s="6"/>
-      <c r="AI187" s="6"/>
-      <c r="AJ187" s="6"/>
-      <c r="AK187" s="6"/>
-      <c r="AL187" s="6"/>
-      <c r="AM187" s="6"/>
-      <c r="AN187" s="9"/>
-      <c r="AO187" s="6"/>
+      <c r="M187" s="5">
+        <v>2791.1999999999998</v>
+      </c>
+      <c r="N187" s="6">
+        <v>33</v>
+      </c>
+      <c r="O187" s="6">
+        <v>24</v>
+      </c>
+      <c r="P187" s="7">
+        <v>8.7409090909090903</v>
+      </c>
+      <c r="Q187" s="8">
+        <v>23.357637499999999</v>
+      </c>
+      <c r="R187" s="8">
+        <v>8.4608695652173918</v>
+      </c>
+      <c r="S187" s="8">
+        <v>7</v>
+      </c>
+      <c r="T187" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="U187" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="V187" s="9">
+        <v>0</v>
+      </c>
+      <c r="W187" s="9">
+        <v>0</v>
+      </c>
+      <c r="X187" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="Y187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="AB187" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="AC187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD187" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO187" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP187" s="4">
         <v>58</v>
       </c>
@@ -32920,137 +33421,282 @@
       </c>
     </row>
     <row r="216" ht="13.5" customHeight="1">
-      <c t="s" r="A216" s="11">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>56</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>57</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>58</v>
+      </c>
+      <c r="L216" s="4"/>
+      <c r="M216" s="5"/>
+      <c r="N216" s="6"/>
+      <c r="O216" s="6">
+        <v>87</v>
+      </c>
+      <c r="P216" s="7"/>
+      <c r="Q216" s="8"/>
+      <c r="R216" s="8"/>
+      <c r="S216" s="8">
+        <v>7</v>
+      </c>
+      <c r="T216" s="9"/>
+      <c r="U216" s="9">
+        <v>0.17241379310344829</v>
+      </c>
+      <c r="V216" s="9">
+        <v>0.011494252873563218</v>
+      </c>
+      <c r="W216" s="9">
+        <v>0</v>
+      </c>
+      <c r="X216" s="9">
+        <v>0.057471264367816091</v>
+      </c>
+      <c r="Y216" s="9">
+        <v>0.011494252873563218</v>
+      </c>
+      <c r="Z216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA216" s="9">
+        <v>0.011494252873563218</v>
+      </c>
+      <c r="AB216" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="AC216" s="9">
+        <v>0.045977011494252873</v>
+      </c>
+      <c r="AD216" s="6">
+        <v>20</v>
+      </c>
+      <c r="AE216" s="6">
+        <v>15</v>
+      </c>
+      <c r="AF216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH216" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL216" s="6">
+        <v>6</v>
+      </c>
+      <c r="AM216" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN216" s="9">
+        <v>0.022988505747126436</v>
+      </c>
+      <c r="AO216" s="6">
+        <v>2</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>58</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>307</v>
       </c>
-      <c t="s" r="B216" s="11">
+      <c t="s" r="AS216" s="4">
+        <v>60</v>
+      </c>
+      <c t="s" r="AT216" s="4">
+        <v>61</v>
+      </c>
+      <c t="s" r="AU216" s="4">
+        <v>62</v>
+      </c>
+      <c t="s" r="AV216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW216" s="4">
+        <v>59</v>
+      </c>
+      <c r="AX216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ216" s="10"/>
+      <c t="s" r="BA216" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="217" ht="13.5" customHeight="1">
+      <c t="s" r="A217" s="11">
         <v>308</v>
       </c>
-      <c r="C216" s="12"/>
-      <c r="D216" s="12"/>
-      <c r="E216" s="12"/>
-      <c r="F216" s="12"/>
-      <c r="G216" s="12"/>
-      <c r="H216" s="12"/>
-      <c r="I216" s="12"/>
-      <c r="J216" s="12"/>
-      <c r="K216" s="12"/>
-      <c r="L216" s="12"/>
-      <c t="s" r="M216" s="11">
+      <c t="s" r="B217" s="11">
         <v>309</v>
       </c>
-      <c t="s" r="N216" s="11">
+      <c r="C217" s="12"/>
+      <c r="D217" s="12"/>
+      <c r="E217" s="12"/>
+      <c r="F217" s="12"/>
+      <c r="G217" s="12"/>
+      <c r="H217" s="12"/>
+      <c r="I217" s="12"/>
+      <c r="J217" s="12"/>
+      <c r="K217" s="12"/>
+      <c r="L217" s="12"/>
+      <c t="s" r="M217" s="11">
         <v>310</v>
       </c>
-      <c t="s" r="O216" s="11">
+      <c t="s" r="N217" s="11">
         <v>311</v>
       </c>
-      <c t="s" r="P216" s="11">
+      <c t="s" r="O217" s="11">
         <v>312</v>
       </c>
-      <c t="s" r="Q216" s="11">
+      <c t="s" r="P217" s="11">
         <v>313</v>
       </c>
-      <c t="s" r="R216" s="11">
+      <c t="s" r="Q217" s="11">
         <v>314</v>
       </c>
-      <c t="s" r="S216" s="11">
+      <c t="s" r="R217" s="11">
         <v>315</v>
       </c>
-      <c t="s" r="T216" s="11">
+      <c t="s" r="S217" s="11">
         <v>316</v>
       </c>
-      <c t="s" r="U216" s="11">
+      <c t="s" r="T217" s="11">
         <v>317</v>
       </c>
-      <c t="s" r="V216" s="11">
+      <c t="s" r="U217" s="11">
         <v>318</v>
       </c>
-      <c t="s" r="W216" s="11">
+      <c t="s" r="V217" s="11">
         <v>319</v>
       </c>
-      <c t="s" r="X216" s="11">
+      <c t="s" r="W217" s="11">
         <v>320</v>
       </c>
-      <c t="s" r="Y216" s="11">
+      <c t="s" r="X217" s="11">
         <v>321</v>
       </c>
-      <c t="s" r="Z216" s="11">
-        <v>319</v>
-      </c>
-      <c t="s" r="AA216" s="11">
+      <c t="s" r="Y217" s="11">
         <v>322</v>
       </c>
-      <c t="s" r="AB216" s="11">
+      <c t="s" r="Z217" s="11">
+        <v>320</v>
+      </c>
+      <c t="s" r="AA217" s="11">
         <v>323</v>
       </c>
-      <c t="s" r="AC216" s="11">
+      <c t="s" r="AB217" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AD216" s="11">
+      <c t="s" r="AC217" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AE216" s="11">
+      <c t="s" r="AD217" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AF216" s="11">
+      <c t="s" r="AE217" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AG216" s="11">
+      <c t="s" r="AF217" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AH216" s="11">
+      <c t="s" r="AG217" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AI216" s="11">
+      <c t="s" r="AH217" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AJ216" s="11">
+      <c t="s" r="AI217" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AK216" s="11">
+      <c t="s" r="AJ217" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AL216" s="11">
+      <c t="s" r="AK217" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AM216" s="11">
+      <c t="s" r="AL217" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AN216" s="11">
+      <c t="s" r="AM217" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AO216" s="11">
+      <c t="s" r="AN217" s="11">
         <v>336</v>
       </c>
-      <c r="AP216" s="12"/>
-      <c t="s" r="AQ216" s="12">
-        <v>59</v>
-      </c>
-      <c r="AR216" s="12"/>
-      <c r="AS216" s="12"/>
-      <c r="AT216" s="12"/>
-      <c r="AU216" s="12"/>
-      <c t="s" r="AV216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AW216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AX216" s="11">
+      <c t="s" r="AO217" s="11">
         <v>337</v>
       </c>
-      <c t="s" r="AY216" s="11">
-        <v>337</v>
-      </c>
-      <c r="AZ216" s="12"/>
-      <c r="BA216" s="12"/>
+      <c r="AP217" s="12"/>
+      <c t="s" r="AQ217" s="12">
+        <v>59</v>
+      </c>
+      <c r="AR217" s="12"/>
+      <c r="AS217" s="12"/>
+      <c r="AT217" s="12"/>
+      <c r="AU217" s="12"/>
+      <c t="s" r="AV217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AX217" s="11">
+        <v>338</v>
+      </c>
+      <c t="s" r="AY217" s="11">
+        <v>338</v>
+      </c>
+      <c r="AZ217" s="12"/>
+      <c r="BA217" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:BA216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:BA217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-11).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-11).xlsx
@@ -938,13 +938,13 @@
     <t>215</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 9.128,90</t>
-  </si>
-  <si>
-    <t>97.5</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 9.149,09</t>
+  </si>
+  <si>
+    <t>97.7</t>
   </si>
   <si>
     <t>61.3</t>
@@ -953,10 +953,10 @@
     <t>6.45</t>
   </si>
   <si>
-    <t>21.4</t>
-  </si>
-  <si>
-    <t>8.2</t>
+    <t>21.5</t>
+  </si>
+  <si>
+    <t>8.3</t>
   </si>
   <si>
     <t>6.2</t>
@@ -25138,7 +25138,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>51</v>
@@ -25168,18 +25168,30 @@
         <v>58</v>
       </c>
       <c r="L159" s="4"/>
-      <c r="M159" s="5"/>
-      <c r="N159" s="6"/>
+      <c r="M159" s="5">
+        <v>12862.6</v>
+      </c>
+      <c r="N159" s="6">
+        <v>123</v>
+      </c>
       <c r="O159" s="6">
         <v>102</v>
       </c>
-      <c r="P159" s="7"/>
-      <c r="Q159" s="8"/>
-      <c r="R159" s="8"/>
+      <c r="P159" s="7">
+        <v>6.3981336000000004</v>
+      </c>
+      <c r="Q159" s="8">
+        <v>34.432352941176468</v>
+      </c>
+      <c r="R159" s="8">
+        <v>20.829738235294116</v>
+      </c>
       <c r="S159" s="8">
         <v>7</v>
       </c>
-      <c r="T159" s="9"/>
+      <c r="T159" s="9">
+        <v>0.029411764705882353</v>
+      </c>
       <c r="U159" s="9">
         <v>0.058823529411764705</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-11).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-11).xlsx
@@ -938,19 +938,19 @@
     <t>215</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 9.149,09</t>
-  </si>
-  <si>
-    <t>97.7</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 9.154,97</t>
+  </si>
+  <si>
+    <t>97.6</t>
   </si>
   <si>
     <t>61.3</t>
   </si>
   <si>
-    <t>6.45</t>
+    <t>6.46</t>
   </si>
   <si>
     <t>21.5</t>
@@ -14722,7 +14722,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14750,14 +14750,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>10243.09</v>
+      </c>
+      <c r="N89" s="6">
+        <v>93</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>7.1789010638297865</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>23.631844642857143</v>
+      </c>
+      <c r="R89" s="8">
+        <v>8.5684854545454545</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.125</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -29096,7 +29108,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>51</v>
@@ -31804,7 +31816,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>51</v>
@@ -33437,7 +33449,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>51</v>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-11).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-11).xlsx
@@ -938,34 +938,34 @@
     <t>215</t>
   </si>
   <si>
-    <t>28</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 9.154,97</t>
+    <t>R$ 9.127,50</t>
   </si>
   <si>
-    <t>97.6</t>
+    <t>97.1</t>
   </si>
   <si>
-    <t>61.3</t>
+    <t>61.8</t>
   </si>
   <si>
-    <t>6.46</t>
+    <t>6.61</t>
   </si>
   <si>
-    <t>21.5</t>
+    <t>21.7</t>
   </si>
   <si>
-    <t>8.3</t>
+    <t>8.4</t>
   </si>
   <si>
-    <t>6.2</t>
+    <t>6.4</t>
   </si>
   <si>
-    <t>33.6%</t>
+    <t>33.0%</t>
   </si>
   <si>
-    <t>16.6%</t>
+    <t>16.2%</t>
   </si>
   <si>
     <t>0.9%</t>
@@ -974,34 +974,34 @@
     <t>0.1%</t>
   </si>
   <si>
-    <t>3.2%</t>
+    <t>3.1%</t>
   </si>
   <si>
     <t>0.7%</t>
   </si>
   <si>
-    <t>6.0%</t>
+    <t>5.8%</t>
   </si>
   <si>
     <t>2.7%</t>
   </si>
   <si>
-    <t>5.5%</t>
+    <t>5.4%</t>
   </si>
   <si>
-    <t>2229.0</t>
+    <t>2256.0</t>
   </si>
   <si>
-    <t>1894.0</t>
+    <t>1921.0</t>
   </si>
   <si>
-    <t>103.0</t>
+    <t>105.0</t>
   </si>
   <si>
     <t>16.0</t>
   </si>
   <si>
-    <t>363.0</t>
+    <t>369.0</t>
   </si>
   <si>
     <t>85.0</t>
@@ -1010,19 +1010,19 @@
     <t>14.0</t>
   </si>
   <si>
-    <t>686.0</t>
+    <t>687.0</t>
   </si>
   <si>
-    <t>310.0</t>
+    <t>315.0</t>
   </si>
   <si>
-    <t>625.0</t>
+    <t>637.0</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
-    <t>43.0</t>
+    <t>44.0</t>
   </si>
   <si>
     <t>1</t>
@@ -2209,7 +2209,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2239,35 +2239,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>14034.59</v>
+      </c>
+      <c r="N6" s="6">
+        <v>130</v>
+      </c>
+      <c r="O6" s="6">
+        <v>98</v>
+      </c>
+      <c r="P6" s="7">
+        <v>6.2226100775193798</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>15.603741836734693</v>
+      </c>
+      <c r="R6" s="8">
+        <v>2.5454081632653058</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.040816326530612242</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.040816326530612242</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -9078,7 +9136,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9108,14 +9166,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>1115.02</v>
+      </c>
+      <c r="N51" s="6">
+        <v>10</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>6.4249999999999998</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>32.111899999999999</v>
+      </c>
+      <c r="R51" s="8">
+        <v>19.216671428571427</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -10147,33 +10217,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>88</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.079545454545454544</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0.011363636363636364</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -24070,7 +24186,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -24100,35 +24216,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>8479.4899999999998</v>
+      </c>
+      <c r="N151" s="6">
+        <v>100</v>
+      </c>
+      <c r="O151" s="6">
+        <v>90</v>
+      </c>
+      <c r="P151" s="7">
+        <v>29.624411111111108</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>52.559258888888891</v>
+      </c>
+      <c r="R151" s="8">
+        <v>14.817407777777779</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.088888888888888892</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.011111111111111112</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.011111111111111112</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -24952,7 +25126,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -24982,35 +25156,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>5478.0799999999999</v>
+      </c>
+      <c r="N157" s="6">
+        <v>63</v>
+      </c>
+      <c r="O157" s="6">
+        <v>53</v>
+      </c>
+      <c r="P157" s="7">
+        <v>7.6462370967741942</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>19.471069811320753</v>
+      </c>
+      <c r="R157" s="8">
+        <v>4.7018867924528296</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.15094339622641509</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0.056603773584905662</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0.056603773584905662</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -25051,7 +25283,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25081,35 +25313,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>6822.04</v>
+      </c>
+      <c r="N158" s="6">
+        <v>60</v>
+      </c>
+      <c r="O158" s="6">
+        <v>54</v>
+      </c>
+      <c r="P158" s="7">
+        <v>5.607527419354839</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>18.777777777777779</v>
+      </c>
+      <c r="R158" s="8">
+        <v>6.317283333333334</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0.018518518518518517</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -26034,7 +26324,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26064,35 +26354,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>13727.030000000001</v>
+      </c>
+      <c r="N165" s="6">
+        <v>112</v>
+      </c>
+      <c r="O165" s="6">
+        <v>82</v>
+      </c>
+      <c r="P165" s="7">
+        <v>13.131211818181818</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>38.106097560975606</v>
+      </c>
+      <c r="R165" s="8">
+        <v>15.55223536585366</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0.10975609756097561</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0.012195121951219513</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0.097560975609756101</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
